--- a/Data/def_firm_sep.xlsx
+++ b/Data/def_firm_sep.xlsx
@@ -1,21 +1,317 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marcel/Documents/GitHub/Stage_BxSE/Data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2AA3735-9BF9-9B4A-B0EA-91B37AA7C5F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$D$1:$D$115</definedName>
+  </definedNames>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="94">
+  <si>
+    <t>Defendants</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>Country_Defendants</t>
+  </si>
+  <si>
+    <t>NPE</t>
+  </si>
+  <si>
+    <t>Oleading B.V.</t>
+  </si>
+  <si>
+    <t>NL</t>
+  </si>
+  <si>
+    <t>Realme Germany GmbH</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>Reflection Investment B.V.</t>
+  </si>
+  <si>
+    <t>Xiaomi</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>OTECH Italia S.r.l.</t>
+  </si>
+  <si>
+    <t>Oppo</t>
+  </si>
+  <si>
+    <t>OnePlus Technology (Shenzhen) Co., Ltd</t>
+  </si>
+  <si>
+    <t>Vantiva</t>
+  </si>
+  <si>
+    <t>FR</t>
+  </si>
+  <si>
+    <t>TP-LINK</t>
+  </si>
+  <si>
+    <t>ASD SAS</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>Meta Platforms, Inc.</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>Hisense GmbH</t>
+  </si>
+  <si>
+    <t>AB S.A.</t>
+  </si>
+  <si>
+    <t>PL</t>
+  </si>
+  <si>
+    <t>ATAG Nederland</t>
+  </si>
+  <si>
+    <t>Tekpoint GmbH</t>
+  </si>
+  <si>
+    <t>Gorenje gospodinjski aparati, d.o.o</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>Tecno Mobile Ltd.</t>
+  </si>
+  <si>
+    <t>HK</t>
+  </si>
+  <si>
+    <t>Shenzhen Transsion Holdings Co., Ltd.</t>
+  </si>
+  <si>
+    <t>Infinix Mobility Ltd.</t>
+  </si>
+  <si>
+    <t>Verifone</t>
+  </si>
+  <si>
+    <t>NTT System S.A.</t>
+  </si>
+  <si>
+    <t>Itel Mobile Ltd.</t>
+  </si>
+  <si>
+    <t>Galaxus Deutschland GmbH</t>
+  </si>
+  <si>
+    <t>EC Cash Direkt GmbH</t>
+  </si>
+  <si>
+    <t>Adyen N.V.</t>
+  </si>
+  <si>
+    <t>Egenta s.r.o.</t>
+  </si>
+  <si>
+    <t>CZ</t>
+  </si>
+  <si>
+    <t>Samsung</t>
+  </si>
+  <si>
+    <t>KR</t>
+  </si>
+  <si>
+    <t>Motorola</t>
+  </si>
+  <si>
+    <t>Lenovo</t>
+  </si>
+  <si>
+    <t>MediaTek Inc.</t>
+  </si>
+  <si>
+    <t>TW</t>
+  </si>
+  <si>
+    <t>The Walt Disney Company</t>
+  </si>
+  <si>
+    <t>Facebook</t>
+  </si>
+  <si>
+    <t>Roku, Inc.</t>
+  </si>
+  <si>
+    <t>Netgear</t>
+  </si>
+  <si>
+    <t>RTL Group</t>
+  </si>
+  <si>
+    <t>LU</t>
+  </si>
+  <si>
+    <t>HEWLETT-PACKARD</t>
+  </si>
+  <si>
+    <t>Bedrock S.A.S.</t>
+  </si>
+  <si>
+    <t>CO</t>
+  </si>
+  <si>
+    <t>Yimi S.r.l</t>
+  </si>
+  <si>
+    <t>Digital River</t>
+  </si>
+  <si>
+    <t>Flanco Retail SA</t>
+  </si>
+  <si>
+    <t>RO</t>
+  </si>
+  <si>
+    <t>OTECH Germany GmbH</t>
+  </si>
+  <si>
+    <t>Netprisma, Inc.</t>
+  </si>
+  <si>
+    <t>Fantasia Trading LLC</t>
+  </si>
+  <si>
+    <t>Wireless Mobility GmbH</t>
+  </si>
+  <si>
+    <t>Acceleronix B.V.</t>
+  </si>
+  <si>
+    <t>Eagle Electronics Inc.</t>
+  </si>
+  <si>
+    <t>Anker Innovations</t>
+  </si>
+  <si>
+    <t>Belkin</t>
+  </si>
+  <si>
+    <t>Eagle Wireless Inc.</t>
+  </si>
+  <si>
+    <t>Quectel Wireless</t>
+  </si>
+  <si>
+    <t>Huawei</t>
+  </si>
+  <si>
+    <t>Ericsson</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>TCL</t>
+  </si>
+  <si>
+    <t>MK TRADE SIA</t>
+  </si>
+  <si>
+    <t>FI</t>
+  </si>
+  <si>
+    <t>Texas Instruments</t>
+  </si>
+  <si>
+    <t>Qualcomm</t>
+  </si>
+  <si>
+    <t>CCV Group B.V.</t>
+  </si>
+  <si>
+    <t>Lotus Cars</t>
+  </si>
+  <si>
+    <t>GB</t>
+  </si>
+  <si>
+    <t>EC Cash Direkt</t>
+  </si>
+  <si>
+    <t>Sunmi Technology</t>
+  </si>
+  <si>
+    <t>Zeekr Germany GmbH</t>
+  </si>
+  <si>
+    <t>smart Europe GmbH</t>
+  </si>
+  <si>
+    <t>Lynk &amp; Co</t>
+  </si>
+  <si>
+    <t>Odiporo</t>
+  </si>
+  <si>
+    <t>Shamrock Mobile</t>
+  </si>
+  <si>
+    <t>Max ICT B.V.</t>
+  </si>
+  <si>
+    <t>ZTE Corporation</t>
+  </si>
+  <si>
+    <t>BYD</t>
+  </si>
+  <si>
+    <t>ZEEKR Germany GmbH</t>
+  </si>
+  <si>
+    <t>Vivo Mobile</t>
+  </si>
+  <si>
+    <t>Smart Europe GmbH</t>
+  </si>
+  <si>
+    <t>ASUS</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +359,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +411,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +445,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +480,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,577 +656,451 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:D115"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="33" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Defendants</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Country_Defendants</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>NPE</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Oleading B.V.</t>
-        </is>
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>4</v>
       </c>
       <c r="B2">
         <v>2025</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
+      <c r="C2" t="s">
+        <v>5</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Realme Germany GmbH</t>
-        </is>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>6</v>
       </c>
       <c r="B3">
         <v>2025</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
+      <c r="C3" t="s">
+        <v>7</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Reflection Investment B.V.</t>
-        </is>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>8</v>
       </c>
       <c r="B4">
         <v>2025</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
+      <c r="C4" t="s">
+        <v>5</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Xiaomi</t>
-        </is>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>9</v>
       </c>
       <c r="B5">
         <v>2025</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
+      <c r="C5" t="s">
+        <v>10</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>OTECH Italia S.r.l.</t>
-        </is>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>11</v>
       </c>
       <c r="B6">
         <v>2025</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
+      <c r="C6" t="s">
+        <v>7</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Oppo</t>
-        </is>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>12</v>
       </c>
       <c r="B7">
         <v>2025</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
+      <c r="C7" t="s">
+        <v>10</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>OnePlus Technology (Shenzhen) Co., Ltd</t>
-        </is>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>13</v>
       </c>
       <c r="B8">
         <v>2025</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
+      <c r="C8" t="s">
+        <v>10</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Xiaomi</t>
-        </is>
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>9</v>
       </c>
       <c r="B9">
         <v>2024</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
+      <c r="C9" t="s">
+        <v>10</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Xiaomi</t>
-        </is>
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>9</v>
       </c>
       <c r="B10">
         <v>2025</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
+      <c r="C10" t="s">
+        <v>10</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Vantiva</t>
-        </is>
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>14</v>
       </c>
       <c r="B11">
         <v>2024</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
+      <c r="C11" t="s">
+        <v>15</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TP-LINK</t>
-        </is>
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>16</v>
       </c>
       <c r="B12">
         <v>2024</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
+      <c r="C12" t="s">
+        <v>10</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>OTECH Italia S.r.l.</t>
-        </is>
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>11</v>
       </c>
       <c r="B13">
         <v>2025</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
+      <c r="C13" t="s">
+        <v>7</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Reflection Investment B.V.</t>
-        </is>
+    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>8</v>
       </c>
       <c r="B14">
         <v>2025</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
+      <c r="C14" t="s">
+        <v>5</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Oleading B.V.</t>
-        </is>
+    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>4</v>
       </c>
       <c r="B15">
         <v>2025</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
+      <c r="C15" t="s">
+        <v>5</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Oppo</t>
-        </is>
+    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>12</v>
       </c>
       <c r="B16">
         <v>2025</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
+      <c r="C16" t="s">
+        <v>10</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Realme Germany GmbH</t>
-        </is>
+    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>6</v>
       </c>
       <c r="B17">
         <v>2025</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
+      <c r="C17" t="s">
+        <v>7</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ASD SAS</t>
-        </is>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>17</v>
       </c>
       <c r="B18">
         <v>2025</v>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
+      <c r="C18" t="s">
+        <v>18</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>19</v>
       </c>
       <c r="B19">
         <v>2025</v>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
+      <c r="C19" t="s">
+        <v>20</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Hisense GmbH</t>
-        </is>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>21</v>
       </c>
       <c r="B20">
         <v>2025</v>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
+      <c r="C20" t="s">
+        <v>7</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>AB S.A.</t>
-        </is>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>22</v>
       </c>
       <c r="B21">
         <v>2025</v>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
+      <c r="C21" t="s">
+        <v>23</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>ATAG Nederland</t>
-        </is>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>24</v>
       </c>
       <c r="B22">
         <v>2025</v>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
+      <c r="C22" t="s">
+        <v>5</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Tekpoint GmbH</t>
-        </is>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>25</v>
       </c>
       <c r="B23">
         <v>2025</v>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
+      <c r="C23" t="s">
+        <v>7</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Gorenje gospodinjski aparati, d.o.o</t>
-        </is>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>26</v>
       </c>
       <c r="B24">
         <v>2025</v>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
+      <c r="C24" t="s">
+        <v>27</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Tecno Mobile Ltd.</t>
-        </is>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>28</v>
       </c>
       <c r="B25">
         <v>2025</v>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
+      <c r="C25" t="s">
+        <v>29</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Shenzhen Transsion Holdings Co., Ltd.</t>
-        </is>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>30</v>
       </c>
       <c r="B26">
         <v>2025</v>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
+      <c r="C26" t="s">
+        <v>10</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Infinix Mobility Ltd.</t>
-        </is>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>31</v>
       </c>
       <c r="B27">
         <v>2025</v>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
+      <c r="C27" t="s">
+        <v>29</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Verifone</t>
-        </is>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>32</v>
       </c>
       <c r="B28">
         <v>2026</v>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
+      <c r="C28" t="s">
+        <v>20</v>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>NTT System S.A.</t>
-        </is>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>33</v>
       </c>
       <c r="B29">
         <v>2025</v>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
+      <c r="C29" t="s">
+        <v>23</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Itel Mobile Ltd.</t>
-        </is>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>34</v>
       </c>
       <c r="B30">
         <v>2025</v>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
+      <c r="C30" t="s">
+        <v>29</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Galaxus Deutschland GmbH</t>
-        </is>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>35</v>
       </c>
       <c r="B31">
         <v>2025</v>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
+      <c r="C31" t="s">
+        <v>7</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>EC Cash Direkt GmbH</t>
-        </is>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>36</v>
       </c>
       <c r="B32">
         <v>2026</v>
@@ -929,281 +1109,219 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Adyen N.V.</t>
-        </is>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>37</v>
       </c>
       <c r="B33">
         <v>2026</v>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
+      <c r="C33" t="s">
+        <v>5</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Egenta s.r.o.</t>
-        </is>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>38</v>
       </c>
       <c r="B34">
         <v>2025</v>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>CZ</t>
-        </is>
+      <c r="C34" t="s">
+        <v>39</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
+    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>40</v>
       </c>
       <c r="B35">
         <v>2024</v>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
+      <c r="C35" t="s">
+        <v>41</v>
       </c>
       <c r="D35">
         <v>1</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Xiaomi</t>
-        </is>
+    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>9</v>
       </c>
       <c r="B36">
         <v>2026</v>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
+      <c r="C36" t="s">
+        <v>10</v>
       </c>
       <c r="D36">
         <v>1</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>42</v>
       </c>
       <c r="B37">
         <v>2025</v>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
+      <c r="C37" t="s">
+        <v>20</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Lenovo</t>
-        </is>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>43</v>
       </c>
       <c r="B38">
         <v>2025</v>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
+      <c r="C38" t="s">
+        <v>29</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>MediaTek Inc.</t>
-        </is>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>44</v>
       </c>
       <c r="B39">
         <v>2025</v>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>TW</t>
-        </is>
+      <c r="C39" t="s">
+        <v>45</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>The Walt Disney Company</t>
-        </is>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>46</v>
       </c>
       <c r="B40">
         <v>2026</v>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
+      <c r="C40" t="s">
+        <v>20</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>47</v>
       </c>
       <c r="B41">
         <v>2026</v>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
+      <c r="C41" t="s">
+        <v>20</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Roku, Inc.</t>
-        </is>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>48</v>
       </c>
       <c r="B42">
         <v>2025</v>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
+      <c r="C42" t="s">
+        <v>20</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Netgear</t>
-        </is>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>49</v>
       </c>
       <c r="B43">
         <v>2023</v>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
+      <c r="C43" t="s">
+        <v>20</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>RTL Group</t>
-        </is>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>50</v>
       </c>
       <c r="B44">
         <v>2026</v>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
+      <c r="C44" t="s">
+        <v>51</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>HEWLETT-PACKARD</t>
-        </is>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>52</v>
       </c>
       <c r="B45">
         <v>2025</v>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
+      <c r="C45" t="s">
+        <v>20</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Bedrock S.A.S.</t>
-        </is>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>53</v>
       </c>
       <c r="B46">
         <v>2026</v>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
+      <c r="C46" t="s">
+        <v>54</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
+    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>42</v>
       </c>
       <c r="B47">
         <v>2024</v>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
+      <c r="C47" t="s">
+        <v>20</v>
       </c>
       <c r="D47">
         <v>1</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Yimi S.r.l</t>
-        </is>
+    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>55</v>
       </c>
       <c r="B48">
         <v>2025</v>
@@ -1212,173 +1330,135 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Digital River</t>
-        </is>
+    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>56</v>
       </c>
       <c r="B49">
         <v>2024</v>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
+      <c r="C49" t="s">
+        <v>20</v>
       </c>
       <c r="D49">
         <v>1</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Lenovo</t>
-        </is>
+    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>43</v>
       </c>
       <c r="B50">
         <v>2024</v>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
+      <c r="C50" t="s">
+        <v>29</v>
       </c>
       <c r="D50">
         <v>1</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Tecno Mobile Ltd.</t>
-        </is>
+    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>28</v>
       </c>
       <c r="B51">
         <v>2025</v>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
+      <c r="C51" t="s">
+        <v>29</v>
       </c>
       <c r="D51">
         <v>1</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Tekpoint GmbH</t>
-        </is>
+    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>25</v>
       </c>
       <c r="B52">
         <v>2025</v>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
+      <c r="C52" t="s">
+        <v>7</v>
       </c>
       <c r="D52">
         <v>1</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Flanco Retail SA</t>
-        </is>
+    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>57</v>
       </c>
       <c r="B53">
         <v>2025</v>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
+      <c r="C53" t="s">
+        <v>58</v>
       </c>
       <c r="D53">
         <v>1</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>The Walt Disney Company</t>
-        </is>
+    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>46</v>
       </c>
       <c r="B54">
         <v>2025</v>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
+      <c r="C54" t="s">
+        <v>20</v>
       </c>
       <c r="D54">
         <v>1</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Shenzhen Transsion Holdings Co., Ltd.</t>
-        </is>
+    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>30</v>
       </c>
       <c r="B55">
         <v>2025</v>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
+      <c r="C55" t="s">
+        <v>10</v>
       </c>
       <c r="D55">
         <v>1</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Infinix Mobility Ltd.</t>
-        </is>
+    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>31</v>
       </c>
       <c r="B56">
         <v>2025</v>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
+      <c r="C56" t="s">
+        <v>29</v>
       </c>
       <c r="D56">
         <v>1</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Oleading B.V.</t>
-        </is>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>4</v>
       </c>
       <c r="B57">
         <v>2024</v>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
+      <c r="C57" t="s">
+        <v>5</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>OTECH Germany GmbH</t>
-        </is>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>59</v>
       </c>
       <c r="B58">
         <v>2024</v>
@@ -1387,875 +1467,681 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Oppo</t>
-        </is>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>12</v>
       </c>
       <c r="B59">
         <v>2024</v>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
+      <c r="C59" t="s">
+        <v>10</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Reflection Investment B.V.</t>
-        </is>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>8</v>
       </c>
       <c r="B60">
         <v>2024</v>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
+      <c r="C60" t="s">
+        <v>5</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Netprisma, Inc.</t>
-        </is>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>60</v>
       </c>
       <c r="B61">
         <v>2025</v>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
+      <c r="C61" t="s">
+        <v>20</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Fantasia Trading LLC</t>
-        </is>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>61</v>
       </c>
       <c r="B62">
         <v>2025</v>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
+      <c r="C62" t="s">
+        <v>20</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Wireless Mobility GmbH</t>
-        </is>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>62</v>
       </c>
       <c r="B63">
         <v>2025</v>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
+      <c r="C63" t="s">
+        <v>7</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Acceleronix B.V.</t>
-        </is>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>63</v>
       </c>
       <c r="B64">
         <v>2025</v>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
+      <c r="C64" t="s">
+        <v>5</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Eagle Electronics Inc.</t>
-        </is>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>64</v>
       </c>
       <c r="B65">
         <v>2025</v>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
+      <c r="C65" t="s">
+        <v>20</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Anker Innovations</t>
-        </is>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>65</v>
       </c>
       <c r="B66">
         <v>2025</v>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
+      <c r="C66" t="s">
+        <v>20</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Belkin</t>
-        </is>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>66</v>
       </c>
       <c r="B67">
         <v>2023</v>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
+      <c r="C67" t="s">
+        <v>20</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Eagle Wireless Inc.</t>
-        </is>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>67</v>
       </c>
       <c r="B68">
         <v>2025</v>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
+      <c r="C68" t="s">
+        <v>20</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Quectel Wireless</t>
-        </is>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>68</v>
       </c>
       <c r="B69">
         <v>2025</v>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
+      <c r="C69" t="s">
+        <v>10</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Oppo</t>
-        </is>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>12</v>
       </c>
       <c r="B70">
         <v>2026</v>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
+      <c r="C70" t="s">
+        <v>10</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Belkin</t>
-        </is>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>66</v>
       </c>
       <c r="B71">
         <v>2025</v>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
+      <c r="C71" t="s">
+        <v>20</v>
       </c>
       <c r="D71">
         <v>0</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Oleading B.V.</t>
-        </is>
+    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>4</v>
       </c>
       <c r="B72">
         <v>2026</v>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
+      <c r="C72" t="s">
+        <v>5</v>
       </c>
       <c r="D72">
         <v>1</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Realme Germany GmbH</t>
-        </is>
+    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>6</v>
       </c>
       <c r="B73">
         <v>2026</v>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
+      <c r="C73" t="s">
+        <v>7</v>
       </c>
       <c r="D73">
         <v>1</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Oppo</t>
-        </is>
+    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>12</v>
       </c>
       <c r="B74">
         <v>2026</v>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
+      <c r="C74" t="s">
+        <v>10</v>
       </c>
       <c r="D74">
         <v>1</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>OnePlus Technology (Shenzhen) Co., Ltd</t>
-        </is>
+    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>13</v>
       </c>
       <c r="B75">
         <v>2026</v>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
+      <c r="C75" t="s">
+        <v>10</v>
       </c>
       <c r="D75">
         <v>1</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>OTECH Italia S.r.l.</t>
-        </is>
+    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>11</v>
       </c>
       <c r="B76">
         <v>2026</v>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
+      <c r="C76" t="s">
+        <v>7</v>
       </c>
       <c r="D76">
         <v>1</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Reflection Investment B.V.</t>
-        </is>
+    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>8</v>
       </c>
       <c r="B77">
         <v>2026</v>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
+      <c r="C77" t="s">
+        <v>5</v>
       </c>
       <c r="D77">
         <v>1</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Huawei</t>
-        </is>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>69</v>
       </c>
       <c r="B78">
         <v>2025</v>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
+      <c r="C78" t="s">
+        <v>10</v>
       </c>
       <c r="D78">
         <v>0</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Ericsson</t>
-        </is>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>70</v>
       </c>
       <c r="B79">
         <v>2024</v>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
+      <c r="C79" t="s">
+        <v>71</v>
       </c>
       <c r="D79">
         <v>0</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>TCL</t>
-        </is>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>72</v>
       </c>
       <c r="B80">
         <v>2023</v>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
+      <c r="C80" t="s">
+        <v>10</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>MK TRADE SIA</t>
-        </is>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>73</v>
       </c>
       <c r="B81">
         <v>2025</v>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>FI</t>
-        </is>
+      <c r="C81" t="s">
+        <v>74</v>
       </c>
       <c r="D81">
         <v>0</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>TCL</t>
-        </is>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>72</v>
       </c>
       <c r="B82">
         <v>2024</v>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
+      <c r="C82" t="s">
+        <v>10</v>
       </c>
       <c r="D82">
         <v>0</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Texas Instruments</t>
-        </is>
+    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>75</v>
       </c>
       <c r="B83">
         <v>2024</v>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
+      <c r="C83" t="s">
+        <v>20</v>
       </c>
       <c r="D83">
         <v>1</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Qualcomm</t>
-        </is>
+    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>76</v>
       </c>
       <c r="B84">
         <v>2024</v>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
+      <c r="C84" t="s">
+        <v>20</v>
       </c>
       <c r="D84">
         <v>1</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>CCV Group B.V.</t>
-        </is>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>77</v>
       </c>
       <c r="B85">
         <v>2024</v>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
+      <c r="C85" t="s">
+        <v>5</v>
       </c>
       <c r="D85">
         <v>0</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Verifone</t>
-        </is>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>32</v>
       </c>
       <c r="B86">
         <v>2024</v>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
+      <c r="C86" t="s">
+        <v>20</v>
       </c>
       <c r="D86">
         <v>0</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Lotus Cars</t>
-        </is>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>78</v>
       </c>
       <c r="B87">
         <v>2025</v>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
+      <c r="C87" t="s">
+        <v>79</v>
       </c>
       <c r="D87">
         <v>0</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>EC Cash Direkt</t>
-        </is>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>80</v>
       </c>
       <c r="B88">
         <v>2024</v>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
+      <c r="C88" t="s">
+        <v>7</v>
       </c>
       <c r="D88">
         <v>0</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Sunmi Technology</t>
-        </is>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>81</v>
       </c>
       <c r="B89">
         <v>2025</v>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
+      <c r="C89" t="s">
+        <v>10</v>
       </c>
       <c r="D89">
         <v>0</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Zeekr Germany GmbH</t>
-        </is>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>82</v>
       </c>
       <c r="B90">
         <v>2025</v>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
+      <c r="C90" t="s">
+        <v>7</v>
       </c>
       <c r="D90">
         <v>0</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>smart Europe GmbH</t>
-        </is>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>83</v>
       </c>
       <c r="B91">
         <v>2025</v>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
+      <c r="C91" t="s">
+        <v>7</v>
       </c>
       <c r="D91">
         <v>0</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Lynk &amp; Co</t>
-        </is>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>84</v>
       </c>
       <c r="B92">
         <v>2025</v>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
+      <c r="C92" t="s">
+        <v>10</v>
       </c>
       <c r="D92">
         <v>0</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Odiporo</t>
-        </is>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>85</v>
       </c>
       <c r="B93">
         <v>2023</v>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
+      <c r="C93" t="s">
+        <v>7</v>
       </c>
       <c r="D93">
         <v>0</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Xiaomi</t>
-        </is>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>9</v>
       </c>
       <c r="B94">
         <v>2024</v>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
+      <c r="C94" t="s">
+        <v>10</v>
       </c>
       <c r="D94">
         <v>0</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Xiaomi</t>
-        </is>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>9</v>
       </c>
       <c r="B95">
         <v>2023</v>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
+      <c r="C95" t="s">
+        <v>10</v>
       </c>
       <c r="D95">
         <v>0</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Shamrock Mobile</t>
-        </is>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>86</v>
       </c>
       <c r="B96">
         <v>2023</v>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
+      <c r="C96" t="s">
+        <v>7</v>
       </c>
       <c r="D96">
         <v>0</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Oppo</t>
-        </is>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>12</v>
       </c>
       <c r="B97">
         <v>2023</v>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
+      <c r="C97" t="s">
+        <v>10</v>
       </c>
       <c r="D97">
         <v>0</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Galaxus Deutschland GmbH</t>
-        </is>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>35</v>
       </c>
       <c r="B98">
         <v>2024</v>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
+      <c r="C98" t="s">
+        <v>7</v>
       </c>
       <c r="D98">
         <v>0</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Tekpoint GmbH</t>
-        </is>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>25</v>
       </c>
       <c r="B99">
         <v>2024</v>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
+      <c r="C99" t="s">
+        <v>7</v>
       </c>
       <c r="D99">
         <v>0</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Shenzhen Transsion Holdings Co., Ltd.</t>
-        </is>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>30</v>
       </c>
       <c r="B100">
         <v>2024</v>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
+      <c r="C100" t="s">
+        <v>10</v>
       </c>
       <c r="D100">
         <v>0</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Max ICT B.V.</t>
-        </is>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>87</v>
       </c>
       <c r="B101">
         <v>2024</v>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
+      <c r="C101" t="s">
+        <v>5</v>
       </c>
       <c r="D101">
         <v>0</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Infinix Mobility Ltd.</t>
-        </is>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>31</v>
       </c>
       <c r="B102">
         <v>2024</v>
       </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
+      <c r="C102" t="s">
+        <v>29</v>
       </c>
       <c r="D102">
         <v>0</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Itel Mobile Ltd.</t>
-        </is>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>34</v>
       </c>
       <c r="B103">
         <v>2024</v>
       </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
+      <c r="C103" t="s">
+        <v>29</v>
       </c>
       <c r="D103">
         <v>0</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Tecno Mobile Ltd.</t>
-        </is>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>28</v>
       </c>
       <c r="B104">
         <v>2024</v>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
+      <c r="C104" t="s">
+        <v>29</v>
       </c>
       <c r="D104">
         <v>0</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>ZTE Corporation</t>
-        </is>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>88</v>
       </c>
       <c r="B105">
         <v>2025</v>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
+      <c r="C105" t="s">
+        <v>10</v>
       </c>
       <c r="D105">
         <v>0</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>BYD</t>
-        </is>
+    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>89</v>
       </c>
       <c r="B106">
         <v>2025</v>
       </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
+      <c r="C106" t="s">
+        <v>10</v>
       </c>
       <c r="D106">
         <v>1</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>ZEEKR Germany GmbH</t>
-        </is>
+    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>90</v>
       </c>
       <c r="B107">
         <v>2025</v>
@@ -2264,65 +2150,51 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Lotus Cars</t>
-        </is>
+    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>78</v>
       </c>
       <c r="B108">
         <v>2025</v>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
+      <c r="C108" t="s">
+        <v>79</v>
       </c>
       <c r="D108">
         <v>1</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Vivo Mobile</t>
-        </is>
+    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>91</v>
       </c>
       <c r="B109">
         <v>2025</v>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
+      <c r="C109" t="s">
+        <v>10</v>
       </c>
       <c r="D109">
         <v>1</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Lynk &amp; Co</t>
-        </is>
+    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>84</v>
       </c>
       <c r="B110">
         <v>2025</v>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
+      <c r="C110" t="s">
+        <v>10</v>
       </c>
       <c r="D110">
         <v>1</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Smart Europe GmbH</t>
-        </is>
+    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>92</v>
       </c>
       <c r="B111">
         <v>2025</v>
@@ -2331,79 +2203,70 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>The Walt Disney Company</t>
-        </is>
+    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>46</v>
       </c>
       <c r="B112">
         <v>2026</v>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
+      <c r="C112" t="s">
+        <v>20</v>
       </c>
       <c r="D112">
         <v>1</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>ASUS</t>
-        </is>
+    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>93</v>
       </c>
       <c r="B113">
         <v>2025</v>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>TW</t>
-        </is>
+      <c r="C113" t="s">
+        <v>45</v>
       </c>
       <c r="D113">
         <v>1</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>40</v>
       </c>
       <c r="B114">
         <v>2024</v>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
+      <c r="C114" t="s">
+        <v>41</v>
       </c>
       <c r="D114">
         <v>0</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>40</v>
       </c>
       <c r="B115">
         <v>2025</v>
       </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
+      <c r="C115" t="s">
+        <v>41</v>
       </c>
       <c r="D115">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="D1:D115" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="0"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>